--- a/inst/extdata/medidor_test/10%_interval/Measurements_10_1.xlsx
+++ b/inst/extdata/medidor_test/10%_interval/Measurements_10_1.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -437,17 +437,17 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>cGSD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>EstLength</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Comments</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H2">
@@ -509,6 +509,11 @@
       <c r="K2">
         <v>0</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M2">
         <v>6.4</v>
       </c>
@@ -523,11 +528,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>0.01</v>
       </c>
-      <c r="R2">
-        <v>13.71</v>
+      <c r="S2">
+        <v>13.75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -535,7 +540,7 @@
         </is>
       </c>
       <c r="U2">
-        <v>1168.13</v>
+        <v>1171.56</v>
       </c>
     </row>
     <row r="3">
@@ -571,7 +576,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H3">
@@ -586,6 +591,11 @@
       <c r="K3">
         <v>0</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M3">
         <v>6.4</v>
       </c>
@@ -600,11 +610,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>0.01</v>
       </c>
-      <c r="R3">
-        <v>1.8</v>
+      <c r="S3">
+        <v>1.89</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -612,7 +622,7 @@
         </is>
       </c>
       <c r="U3">
-        <v>153.33</v>
+        <v>160.71</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +658,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H4">
@@ -663,6 +673,11 @@
       <c r="K4">
         <v>0</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M4">
         <v>6.4</v>
       </c>
@@ -677,11 +692,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>0.01</v>
       </c>
-      <c r="R4">
-        <v>2.39</v>
+      <c r="S4">
+        <v>2.59</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -689,7 +704,7 @@
         </is>
       </c>
       <c r="U4">
-        <v>203.97</v>
+        <v>220.92</v>
       </c>
     </row>
     <row r="5">
@@ -725,7 +740,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H5">
@@ -740,6 +755,11 @@
       <c r="K5">
         <v>0</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M5">
         <v>6.4</v>
       </c>
@@ -754,11 +774,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>0.01</v>
       </c>
-      <c r="R5">
-        <v>2.94</v>
+      <c r="S5">
+        <v>3.1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -766,7 +786,7 @@
         </is>
       </c>
       <c r="U5">
-        <v>250.55</v>
+        <v>263.79</v>
       </c>
     </row>
     <row r="6">
@@ -802,7 +822,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H6">
@@ -817,6 +837,11 @@
       <c r="K6">
         <v>0</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M6">
         <v>6.4</v>
       </c>
@@ -831,11 +856,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>0.01</v>
       </c>
-      <c r="R6">
-        <v>2.86</v>
+      <c r="S6">
+        <v>3.11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -843,7 +868,7 @@
         </is>
       </c>
       <c r="U6">
-        <v>243.71</v>
+        <v>265.08</v>
       </c>
     </row>
     <row r="7">
@@ -879,7 +904,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H7">
@@ -894,6 +919,11 @@
       <c r="K7">
         <v>0</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M7">
         <v>6.4</v>
       </c>
@@ -908,11 +938,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>0.01</v>
       </c>
-      <c r="R7">
-        <v>2.8</v>
+      <c r="S7">
+        <v>2.86</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -920,7 +950,7 @@
         </is>
       </c>
       <c r="U7">
-        <v>238.18</v>
+        <v>243.73</v>
       </c>
     </row>
     <row r="8">
@@ -956,7 +986,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H8">
@@ -971,6 +1001,11 @@
       <c r="K8">
         <v>0</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M8">
         <v>6.4</v>
       </c>
@@ -985,11 +1020,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>0.01</v>
       </c>
-      <c r="R8">
-        <v>2.17</v>
+      <c r="S8">
+        <v>2.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -997,7 +1032,7 @@
         </is>
       </c>
       <c r="U8">
-        <v>184.81</v>
+        <v>187.42</v>
       </c>
     </row>
     <row r="9">
@@ -1033,7 +1068,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H9">
@@ -1048,6 +1083,11 @@
       <c r="K9">
         <v>0</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M9">
         <v>6.4</v>
       </c>
@@ -1062,11 +1102,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>0.01</v>
       </c>
-      <c r="R9">
-        <v>1.38</v>
+      <c r="S9">
+        <v>1.45</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1074,7 +1114,7 @@
         </is>
       </c>
       <c r="U9">
-        <v>117.72</v>
+        <v>123.21</v>
       </c>
     </row>
     <row r="10">
@@ -1110,7 +1150,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H10">
@@ -1125,6 +1165,11 @@
       <c r="K10">
         <v>0</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M10">
         <v>6.4</v>
       </c>
@@ -1139,11 +1184,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>0.01</v>
       </c>
-      <c r="R10">
-        <v>0.67</v>
+      <c r="S10">
+        <v>0.72</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1151,7 +1196,7 @@
         </is>
       </c>
       <c r="U10">
-        <v>57.49</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="11">
@@ -1187,7 +1232,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H11">
@@ -1202,6 +1247,11 @@
       <c r="K11">
         <v>0</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M11">
         <v>6.4</v>
       </c>
@@ -1216,11 +1266,11 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>0.01</v>
       </c>
-      <c r="R11">
-        <v>0.8</v>
+      <c r="S11">
+        <v>0.9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1228,7 +1278,7 @@
         </is>
       </c>
       <c r="U11">
-        <v>68.44</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1314,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H12">
@@ -1279,6 +1329,11 @@
       <c r="K12">
         <v>0</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M12">
         <v>6.4</v>
       </c>
@@ -1293,10 +1348,10 @@
           <t>example_whale.png</t>
         </is>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>0.01</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>5.49</v>
       </c>
       <c r="T12" t="inlineStr">
@@ -1305,7 +1360,909 @@
         </is>
       </c>
       <c r="U12">
-        <v>467.74</v>
+        <v>467.58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>0.5</v>
+      </c>
+      <c r="I13">
+        <v>22.5</v>
+      </c>
+      <c r="J13">
+        <v>23</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M13">
+        <v>6.4</v>
+      </c>
+      <c r="N13">
+        <v>2688</v>
+      </c>
+      <c r="O13">
+        <v>7.6</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R13">
+        <v>0.01</v>
+      </c>
+      <c r="S13">
+        <v>13.75</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="U13">
+        <v>1171.56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>0.5</v>
+      </c>
+      <c r="I14">
+        <v>22.5</v>
+      </c>
+      <c r="J14">
+        <v>23</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M14">
+        <v>6.4</v>
+      </c>
+      <c r="N14">
+        <v>2688</v>
+      </c>
+      <c r="O14">
+        <v>7.6</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R14">
+        <v>0.01</v>
+      </c>
+      <c r="S14">
+        <v>1.89</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>WD_10</t>
+        </is>
+      </c>
+      <c r="U14">
+        <v>160.71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H15">
+        <v>0.5</v>
+      </c>
+      <c r="I15">
+        <v>22.5</v>
+      </c>
+      <c r="J15">
+        <v>23</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M15">
+        <v>6.4</v>
+      </c>
+      <c r="N15">
+        <v>2688</v>
+      </c>
+      <c r="O15">
+        <v>7.6</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R15">
+        <v>0.01</v>
+      </c>
+      <c r="S15">
+        <v>2.59</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>WD_20</t>
+        </is>
+      </c>
+      <c r="U15">
+        <v>220.92</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H16">
+        <v>0.5</v>
+      </c>
+      <c r="I16">
+        <v>22.5</v>
+      </c>
+      <c r="J16">
+        <v>23</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M16">
+        <v>6.4</v>
+      </c>
+      <c r="N16">
+        <v>2688</v>
+      </c>
+      <c r="O16">
+        <v>7.6</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R16">
+        <v>0.01</v>
+      </c>
+      <c r="S16">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>WD_30</t>
+        </is>
+      </c>
+      <c r="U16">
+        <v>263.79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H17">
+        <v>0.5</v>
+      </c>
+      <c r="I17">
+        <v>22.5</v>
+      </c>
+      <c r="J17">
+        <v>23</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M17">
+        <v>6.4</v>
+      </c>
+      <c r="N17">
+        <v>2688</v>
+      </c>
+      <c r="O17">
+        <v>7.6</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R17">
+        <v>0.01</v>
+      </c>
+      <c r="S17">
+        <v>3.11</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>WD_40</t>
+        </is>
+      </c>
+      <c r="U17">
+        <v>265.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>22.5</v>
+      </c>
+      <c r="J18">
+        <v>23</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M18">
+        <v>6.4</v>
+      </c>
+      <c r="N18">
+        <v>2688</v>
+      </c>
+      <c r="O18">
+        <v>7.6</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R18">
+        <v>0.01</v>
+      </c>
+      <c r="S18">
+        <v>2.86</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>WD_50</t>
+        </is>
+      </c>
+      <c r="U18">
+        <v>243.73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>22.5</v>
+      </c>
+      <c r="J19">
+        <v>23</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M19">
+        <v>6.4</v>
+      </c>
+      <c r="N19">
+        <v>2688</v>
+      </c>
+      <c r="O19">
+        <v>7.6</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R19">
+        <v>0.01</v>
+      </c>
+      <c r="S19">
+        <v>2.2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>WD_60</t>
+        </is>
+      </c>
+      <c r="U19">
+        <v>187.42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+      <c r="I20">
+        <v>22.5</v>
+      </c>
+      <c r="J20">
+        <v>23</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M20">
+        <v>6.4</v>
+      </c>
+      <c r="N20">
+        <v>2688</v>
+      </c>
+      <c r="O20">
+        <v>7.6</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R20">
+        <v>0.01</v>
+      </c>
+      <c r="S20">
+        <v>1.45</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>WD_70</t>
+        </is>
+      </c>
+      <c r="U20">
+        <v>123.21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H21">
+        <v>0.5</v>
+      </c>
+      <c r="I21">
+        <v>22.5</v>
+      </c>
+      <c r="J21">
+        <v>23</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M21">
+        <v>6.4</v>
+      </c>
+      <c r="N21">
+        <v>2688</v>
+      </c>
+      <c r="O21">
+        <v>7.6</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R21">
+        <v>0.01</v>
+      </c>
+      <c r="S21">
+        <v>0.72</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>WD_80</t>
+        </is>
+      </c>
+      <c r="U21">
+        <v>61.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H22">
+        <v>0.5</v>
+      </c>
+      <c r="I22">
+        <v>22.5</v>
+      </c>
+      <c r="J22">
+        <v>23</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M22">
+        <v>6.4</v>
+      </c>
+      <c r="N22">
+        <v>2688</v>
+      </c>
+      <c r="O22">
+        <v>7.6</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R22">
+        <v>0.01</v>
+      </c>
+      <c r="S22">
+        <v>0.9</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>WD_90</t>
+        </is>
+      </c>
+      <c r="U22">
+        <v>76.31</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H23">
+        <v>0.5</v>
+      </c>
+      <c r="I23">
+        <v>22.5</v>
+      </c>
+      <c r="J23">
+        <v>23</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M23">
+        <v>6.4</v>
+      </c>
+      <c r="N23">
+        <v>2688</v>
+      </c>
+      <c r="O23">
+        <v>7.6</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="R23">
+        <v>0.01</v>
+      </c>
+      <c r="S23">
+        <v>5.49</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>WD_F</t>
+        </is>
+      </c>
+      <c r="U23">
+        <v>467.58</v>
       </c>
     </row>
   </sheetData>
